--- a/testData/PlaceOrder.xlsx
+++ b/testData/PlaceOrder.xlsx
@@ -417,9 +417,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>10001</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1">
         <v>101</v>
@@ -437,9 +437,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>10002</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1">
         <v>102</v>
@@ -457,9 +457,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>10003</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1">
         <v>103</v>
@@ -479,7 +479,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>10004</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1">
         <v>104</v>
@@ -497,9 +497,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>10005</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1">
         <v>105</v>
@@ -517,9 +517,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>10006</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1">
         <v>106</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>10007</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1">
         <v>107</v>
@@ -557,9 +557,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>10008</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1">
         <v>108</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>10009</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1">
         <v>109</v>
@@ -599,7 +599,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>10010</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1">
         <v>110</v>
@@ -619,7 +619,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>10011</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1">
         <v>111</v>
@@ -637,9 +637,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>10012</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1">
         <v>112</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>10013</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1">
         <v>113</v>
@@ -677,9 +677,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>10014</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1">
         <v>114</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>10015</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1">
         <v>115</v>
@@ -717,9 +717,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>10016</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1">
         <v>116</v>
@@ -737,9 +737,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>10017</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1">
         <v>117</v>
@@ -757,9 +757,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>10018</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1">
         <v>118</v>
@@ -777,9 +777,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>10019</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1">
         <v>119</v>
@@ -797,9 +797,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>10020</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1">
         <v>120</v>
@@ -817,9 +817,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>10021</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1">
         <v>121</v>
@@ -837,9 +837,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>10022</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1">
         <v>122</v>
@@ -857,9 +857,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>10023</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1">
         <v>123</v>
@@ -877,9 +877,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>10024</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1">
         <v>124</v>
@@ -899,7 +899,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>10025</v>
+        <v>25</v>
       </c>
       <c r="B26" s="1">
         <v>125</v>
@@ -919,7 +919,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>10026</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1">
         <v>126</v>
@@ -937,9 +937,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>10027</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1">
         <v>127</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>10028</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1">
         <v>128</v>
@@ -977,9 +977,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>10029</v>
+        <v>29</v>
       </c>
       <c r="B30" s="1">
         <v>129</v>
@@ -997,9 +997,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>10030</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1">
         <v>130</v>
